--- a/outputs/daily/hr_rankings_2026-08-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
